--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationLab.xlsx
+++ b/StructureDefinition-SEEHDSObservationLab.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="652">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1391,6 +1391,98 @@
     <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueInteger</t>
+  </si>
+  <si>
+    <t>valueInteger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>valueRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRatio</t>
+  </si>
+  <si>
+    <t>valueRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueSampledData</t>
+  </si>
+  <si>
+    <t>valueSampledData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SampledData
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueTime</t>
+  </si>
+  <si>
+    <t>valueTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1672,6 +1764,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1747,10 +1843,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Applicable age range, if relevant</t>
@@ -2286,12 +2378,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP97"/>
+  <dimension ref="A1:AP107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.16796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.12890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -9551,9 +9643,11 @@
         <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9571,22 +9665,22 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>276</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>440</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>441</v>
+        <v>368</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9611,13 +9705,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9635,7 +9729,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>438</v>
+        <v>364</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9644,7 +9738,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>446</v>
+        <v>371</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9653,62 +9747,64 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>136</v>
+        <v>373</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>447</v>
+        <v>374</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="D62" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K62" t="s" s="2">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>450</v>
+        <v>379</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>451</v>
+        <v>367</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>452</v>
+        <v>368</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>453</v>
+        <v>380</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9733,13 +9829,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9757,16 +9853,16 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>448</v>
+        <v>364</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9775,29 +9871,31 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>456</v>
+        <v>372</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>457</v>
+        <v>373</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>458</v>
+        <v>374</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>459</v>
+        <v>375</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9806,31 +9904,31 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>462</v>
+        <v>379</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>463</v>
+        <v>367</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>464</v>
+        <v>368</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>465</v>
+        <v>380</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9879,16 +9977,16 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>364</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9897,29 +9995,31 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>466</v>
+        <v>373</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>467</v>
+        <v>374</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9937,22 +10037,22 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>276</v>
+        <v>447</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>379</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>367</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>471</v>
+        <v>368</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9977,13 +10077,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10001,7 +10101,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>468</v>
+        <v>364</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10010,7 +10110,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10019,29 +10119,31 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>475</v>
+        <v>372</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>373</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>374</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>478</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10059,22 +10161,22 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>276</v>
+        <v>450</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>379</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>367</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>482</v>
+        <v>368</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>483</v>
+        <v>380</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10099,13 +10201,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10123,7 +10225,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>364</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10132,7 +10234,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10141,29 +10243,31 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>486</v>
+        <v>373</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>374</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10181,21 +10285,23 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>379</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>491</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10243,7 +10349,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10252,7 +10358,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10261,29 +10367,31 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>493</v>
+        <v>372</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>494</v>
+        <v>373</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>374</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>496</v>
+        <v>375</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10301,22 +10409,22 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>379</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
+        <v>367</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>501</v>
+        <v>368</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>502</v>
+        <v>380</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10365,7 +10473,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>364</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10374,7 +10482,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10383,29 +10491,31 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>503</v>
+        <v>372</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>504</v>
+        <v>373</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>505</v>
+        <v>374</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>506</v>
+        <v>375</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10414,31 +10524,31 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>508</v>
+        <v>459</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>509</v>
+        <v>379</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>510</v>
+        <v>367</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>511</v>
+        <v>368</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>512</v>
+        <v>380</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10487,47 +10597,49 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>364</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>514</v>
+        <v>373</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>515</v>
+        <v>374</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10545,19 +10657,23 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>159</v>
+        <v>462</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>160</v>
+        <v>379</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10605,7 +10721,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10614,47 +10730,49 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D70" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10663,21 +10781,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>138</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>196</v>
+        <v>379</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>197</v>
+        <v>367</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10725,80 +10845,80 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>169</v>
+        <v>364</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>138</v>
+        <v>276</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>467</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>198</v>
+        <v>469</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>234</v>
+        <v>470</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10823,13 +10943,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10847,19 +10967,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10868,10 +10988,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>136</v>
+        <v>475</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10880,26 +11000,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -10908,16 +11028,20 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>524</v>
+        <v>276</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>525</v>
+        <v>478</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10941,13 +11065,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10965,16 +11089,16 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -10983,27 +11107,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11014,10 +11138,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11026,16 +11150,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11083,16 +11211,16 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11104,10 +11232,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>528</v>
+        <v>494</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>533</v>
+        <v>495</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11118,10 +11246,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11147,16 +11275,16 @@
         <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>536</v>
+        <v>498</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>537</v>
+        <v>499</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>538</v>
+        <v>150</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11181,13 +11309,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>117</v>
+        <v>500</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11205,7 +11333,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11223,27 +11351,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>458</v>
+        <v>505</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11254,7 +11382,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11269,16 +11397,16 @@
         <v>276</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>547</v>
+        <v>511</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11303,13 +11431,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11327,13 +11455,13 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
@@ -11345,13 +11473,13 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11362,10 +11490,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11388,18 +11516,18 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11447,7 +11575,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11465,27 +11593,27 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11508,16 +11636,20 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>159</v>
+        <v>526</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11565,7 +11697,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11583,27 +11715,27 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11617,28 +11749,28 @@
         <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>184</v>
+        <v>536</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11687,7 +11819,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11699,7 +11831,7 @@
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>105</v>
+        <v>541</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11708,10 +11840,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11722,10 +11854,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11736,7 +11868,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11745,23 +11877,19 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>568</v>
+        <v>159</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>569</v>
+        <v>160</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11809,19 +11937,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>162</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11830,10 +11958,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>573</v>
+        <v>163</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11844,14 +11972,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>545</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>574</v>
+        <v>545</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11867,23 +11995,21 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>508</v>
+        <v>138</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>575</v>
+        <v>196</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>576</v>
+        <v>197</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11931,7 +12057,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>574</v>
+        <v>169</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11943,7 +12069,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11952,10 +12078,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>580</v>
+        <v>163</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11966,42 +12092,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>160</v>
+        <v>548</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12049,19 +12179,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>162</v>
+        <v>550</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12073,7 +12203,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12084,21 +12214,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12110,17 +12240,15 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>138</v>
+        <v>552</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>196</v>
+        <v>553</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12169,19 +12297,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>169</v>
+        <v>551</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>144</v>
+        <v>556</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12190,10 +12318,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>163</v>
+        <v>558</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12204,46 +12332,42 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>138</v>
+        <v>552</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12291,19 +12415,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>144</v>
+        <v>556</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12312,10 +12436,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>136</v>
+        <v>562</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12326,10 +12450,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12337,7 +12461,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>93</v>
@@ -12349,22 +12473,22 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>276</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12391,9 +12515,11 @@
       <c r="X84" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y84" s="2"/>
+      <c r="Y84" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>300</v>
+        <v>569</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12411,10 +12537,10 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>93</v>
@@ -12429,16 +12555,16 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>303</v>
+        <v>571</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>304</v>
+        <v>486</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -12446,10 +12572,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12460,7 +12586,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12469,22 +12595,22 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>367</v>
+        <v>574</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12509,35 +12635,37 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
@@ -12549,31 +12677,29 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>373</v>
+        <v>571</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>374</v>
+        <v>486</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12591,22 +12717,20 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>378</v>
+        <v>450</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>380</v>
+        <v>582</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12655,7 +12779,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12673,27 +12797,27 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>374</v>
+        <v>583</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12719,10 +12843,10 @@
         <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>160</v>
+        <v>585</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>161</v>
+        <v>586</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12773,7 +12897,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>162</v>
+        <v>584</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12785,7 +12909,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12794,10 +12918,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12808,14 +12932,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12831,21 +12955,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>196</v>
+        <v>589</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>197</v>
+        <v>590</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12881,19 +13007,19 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>169</v>
+        <v>588</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12905,7 +13031,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12914,10 +13040,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>163</v>
+        <v>594</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12928,14 +13054,12 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12944,7 +13068,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12953,22 +13077,22 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>387</v>
+        <v>596</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>388</v>
+        <v>597</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>389</v>
+        <v>598</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>390</v>
+        <v>599</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13017,7 +13141,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>169</v>
+        <v>595</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13029,7 +13153,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13038,10 +13162,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>392</v>
+        <v>601</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13055,7 +13179,7 @@
         <v>602</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13066,7 +13190,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13078,19 +13202,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>395</v>
+        <v>536</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>396</v>
+        <v>603</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>397</v>
+        <v>604</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>398</v>
+        <v>605</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>399</v>
+        <v>606</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13139,13 +13263,13 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>400</v>
+        <v>602</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
@@ -13160,10 +13284,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>401</v>
+        <v>607</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>402</v>
+        <v>608</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13174,10 +13298,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13194,30 +13318,26 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>405</v>
+        <v>160</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>406</v>
+        <v>161</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13237,13 +13357,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13261,7 +13381,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>411</v>
+        <v>162</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13273,7 +13393,7 @@
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13282,10 +13402,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>413</v>
+        <v>163</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13296,21 +13416,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13319,21 +13439,21 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>416</v>
+        <v>196</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13381,19 +13501,19 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>419</v>
+        <v>169</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13402,10 +13522,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>421</v>
+        <v>163</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13416,43 +13536,45 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>424</v>
+        <v>548</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O93" t="s" s="2">
-        <v>426</v>
+        <v>234</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13501,19 +13623,19 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>427</v>
+        <v>550</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13522,10 +13644,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>429</v>
+        <v>136</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13536,10 +13658,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13547,7 +13669,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>93</v>
@@ -13562,19 +13684,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>432</v>
+        <v>613</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>434</v>
+        <v>615</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>435</v>
+        <v>616</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13599,13 +13721,11 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13623,10 +13743,10 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>436</v>
+        <v>612</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>93</v>
@@ -13641,16 +13761,16 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>420</v>
+        <v>303</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>437</v>
+        <v>304</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -13658,10 +13778,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13681,22 +13801,22 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>614</v>
+        <v>367</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13721,31 +13841,29 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13754,7 +13872,7 @@
         <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13763,38 +13881,40 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>136</v>
+        <v>373</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>447</v>
+        <v>374</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="D96" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13803,22 +13923,22 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>451</v>
+        <v>367</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>452</v>
+        <v>620</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>619</v>
+        <v>380</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13843,13 +13963,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13867,13 +13987,13 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
@@ -13885,27 +14005,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>456</v>
+        <v>622</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>457</v>
+        <v>373</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>458</v>
+        <v>374</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>459</v>
+        <v>375</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13916,7 +14036,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13928,20 +14048,16 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>621</v>
+        <v>160</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13989,41 +14105,1257 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>620</v>
+        <v>162</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
+      <c r="H98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q101" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="R101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP97">
+  <autoFilter ref="A1:AP107">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14033,7 +15365,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
